--- a/data/trans_camb/IP25-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IP25-Edad-trans_camb.xlsx
@@ -37,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -63,13 +63,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin"/>
-      <bottom style="thin"/>
       <diagonal/>
     </border>
     <border>
@@ -504,7 +497,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K24"/>
+  <dimension ref="A1:H24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -515,9 +508,6 @@
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -533,21 +523,18 @@
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
-      <c r="E1" s="3" t="n"/>
-      <c r="F1" s="3" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>Niño</t>
         </is>
       </c>
-      <c r="G1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
       <c r="H1" s="3" t="n"/>
-      <c r="I1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="J1" s="3" t="n"/>
-      <c r="K1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
@@ -564,37 +551,22 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>2023/2007</t>
+          <t>2012/2007</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
+          <t>2016/2007</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
           <t>2012/2007</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="H2" s="3" t="inlineStr">
         <is>
           <t>2016/2007</t>
-        </is>
-      </c>
-      <c r="H2" s="3" t="inlineStr">
-        <is>
-          <t>2023/2007</t>
-        </is>
-      </c>
-      <c r="I2" s="3" t="inlineStr">
-        <is>
-          <t>2012/2007</t>
-        </is>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>2016/2007</t>
-        </is>
-      </c>
-      <c r="K2" s="3" t="inlineStr">
-        <is>
-          <t>2023/2007</t>
         </is>
       </c>
     </row>
@@ -607,9 +579,6 @@
       <c r="F3" s="2" t="n"/>
       <c r="G3" s="2" t="n"/>
       <c r="H3" s="2" t="n"/>
-      <c r="I3" s="2" t="n"/>
-      <c r="J3" s="2" t="n"/>
-      <c r="K3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -634,37 +603,22 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-50,96</t>
+          <t>15,27</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>15,27</t>
+          <t>16,46</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>16,46</t>
+          <t>10,74</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-45,99</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>10,74</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
           <t>10,76</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>-48,3</t>
         </is>
       </c>
     </row>
@@ -677,47 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-5,62; 15,48</t>
+          <t>-4,41; 15,99</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,65; 14,64</t>
+          <t>-4,35; 15,81</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-58,83; -43,02</t>
+          <t>5,46; 25,33</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5,82; 25,38</t>
+          <t>6,63; 26,52</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>7,1; 26,26</t>
+          <t>3,32; 17,41</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-52,67; -38,57</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>3,38; 17,27</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>3,51; 17,94</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>-53,36; -42,88</t>
+          <t>3,62; 18,12</t>
         </is>
       </c>
     </row>
@@ -740,37 +679,22 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-100,0%</t>
+          <t>33,19%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>33,19%</t>
+          <t>35,79%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>35,79%</t>
+          <t>22,23%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>22,23%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
           <t>22,28%</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
         </is>
       </c>
     </row>
@@ -783,47 +707,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-9,42; 34,85</t>
+          <t>-7,91; 35,36</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-9,86; 33,24</t>
+          <t>-7,91; 35,69</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>10,5; 62,75</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10,76; 64,6</t>
+          <t>12,78; 65,61</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>13,67; 64,81</t>
+          <t>6,38; 39,32</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>6,44; 39,94</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>6,32; 40,42</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
+          <t>6,81; 41,01</t>
         </is>
       </c>
     </row>
@@ -850,37 +759,22 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-97,35</t>
+          <t>3,39</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3,39</t>
+          <t>1,29</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>1,29</t>
+          <t>1,46</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-95,55</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>1,46</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
           <t>0,81</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>-96,45</t>
         </is>
       </c>
     </row>
@@ -893,47 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,95; 1,68</t>
+          <t>-2,86; 1,81</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,97; 2,84</t>
+          <t>-1,94; 2,43</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-98,59; -95,06</t>
+          <t>1,27; 5,9</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,46; 6,1</t>
+          <t>-1,25; 4,06</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,33; 4,04</t>
+          <t>-0,28; 3,16</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-97,25; -92,75</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>-0,07; 3,25</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>-0,88; 2,55</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>-97,51; -94,97</t>
+          <t>-1,17; 2,48</t>
         </is>
       </c>
     </row>
@@ -956,37 +835,22 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-100,0%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>1,52%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
           <t>0,84%</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
         </is>
       </c>
     </row>
@@ -999,47 +863,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-3,03; 1,74</t>
+          <t>-2,91; 1,88</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-2,02; 2,96</t>
+          <t>-1,95; 2,52</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>1,32; 6,34</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,5; 6,57</t>
+          <t>-1,28; 4,32</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-1,3; 4,33</t>
+          <t>-0,29; 3,32</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-0,07; 3,39</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>-0,9; 2,67</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
+          <t>-1,2; 2,59</t>
         </is>
       </c>
     </row>
@@ -1066,37 +915,22 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-98,36</t>
+          <t>2,95</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2,95</t>
+          <t>3,57</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>3,57</t>
+          <t>1,49</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-95,18</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>1,49</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
           <t>1,18</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>-96,69</t>
         </is>
       </c>
     </row>
@@ -1109,47 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,2; 3,04</t>
+          <t>-2,54; 2,45</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,93; 1,43</t>
+          <t>-3,97; 1,59</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-99,5; -95,55</t>
+          <t>-0,18; 6,52</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,38; 6,71</t>
+          <t>0,73; 7,07</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,65; 7,05</t>
+          <t>-0,58; 3,7</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-97,6; -91,64</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>-0,66; 3,69</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>-0,98; 3,35</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>-98,24; -94,61</t>
+          <t>-0,91; 3,4</t>
         </is>
       </c>
     </row>
@@ -1172,37 +991,22 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-100,0%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>1,54%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
           <t>1,22%</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1019,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-2,2; 3,18</t>
+          <t>-2,56; 2,52</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-4,02; 1,44</t>
+          <t>-4,03; 1,64</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-0,14; 7,16</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-0,38; 7,24</t>
+          <t>0,76; 7,69</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,67; 7,78</t>
+          <t>-0,59; 3,91</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>-0,67; 3,9</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>-1,0; 3,51</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
+          <t>-0,93; 3,6</t>
         </is>
       </c>
     </row>
@@ -1282,37 +1071,22 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-97,26</t>
+          <t>0,65</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>0,65</t>
+          <t>-1,2</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>-1,2</t>
+          <t>0,48</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-96,89</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>0,48</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
           <t>-0,14</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>-97,07</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,75; 2,77</t>
+          <t>-2,47; 2,94</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,55; 3,37</t>
+          <t>-1,68; 3,51</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-98,85; -94,72</t>
+          <t>-2,21; 3,25</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,18; 3,06</t>
+          <t>-4,59; 2,02</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-4,52; 1,9</t>
+          <t>-1,54; 2,37</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-98,44; -94,63</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>-1,71; 2,38</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>-2,15; 1,7</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>-98,13; -95,43</t>
+          <t>-2,34; 1,75</t>
         </is>
       </c>
     </row>
@@ -1388,37 +1147,22 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-100,0%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>-1,24%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>-1,24%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>0,5%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
           <t>-0,14%</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-2,8; 2,9</t>
+          <t>-2,52; 3,08</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-1,58; 3,54</t>
+          <t>-1,71; 3,68</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-2,24; 3,42</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-2,24; 3,17</t>
+          <t>-4,7; 2,11</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-4,62; 2,0</t>
+          <t>-1,57; 2,47</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>-1,74; 2,47</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>-2,2; 1,76</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
+          <t>-2,39; 1,83</t>
         </is>
       </c>
     </row>
@@ -1498,37 +1227,22 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-90,31</t>
+          <t>3,72</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>3,72</t>
+          <t>3,79</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>3,79</t>
+          <t>1,32</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-87,54</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>1,32</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
           <t>1,71</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>-88,88</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-3,85; 1,47</t>
+          <t>-3,92; 1,42</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-2,99; 2,18</t>
+          <t>-3,33; 1,96</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-91,9; -88,23</t>
+          <t>1,18; 6,28</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1,28; 6,59</t>
+          <t>1,33; 6,4</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1,31; 6,68</t>
+          <t>-0,55; 3,26</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-89,27; -85,22</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>-0,53; 3,18</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>-0,16; 3,5</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>-90,1; -87,45</t>
+          <t>-0,21; 3,52</t>
         </is>
       </c>
     </row>
@@ -1604,37 +1303,22 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-100,0%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>1,48%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
           <t>1,93%</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1331,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-4,22; 1,66</t>
+          <t>-4,27; 1,6</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-3,26; 2,46</t>
+          <t>-3,66; 2,2</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>1,33; 7,29</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1,43; 7,75</t>
+          <t>1,49; 7,4</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>1,49; 7,84</t>
+          <t>-0,62; 3,7</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>-0,6; 3,63</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>-0,17; 3,98</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
+          <t>-0,27; 3,99</t>
         </is>
       </c>
     </row>
@@ -1701,11 +1370,11 @@
   </sheetData>
   <mergeCells count="9">
     <mergeCell ref="A4:A7"/>
-    <mergeCell ref="C1:E1"/>
     <mergeCell ref="A8:A11"/>
-    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="E1:F1"/>
     <mergeCell ref="A12:A15"/>
-    <mergeCell ref="I1:K1"/>
     <mergeCell ref="A20:A23"/>
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="A16:A19"/>

--- a/data/trans_camb/IP25-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IP25-Edad-trans_camb.xlsx
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-4,41; 15,99</t>
+          <t>-5,31; 15,2</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-4,35; 15,81</t>
+          <t>-6,2; 15,33</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5,46; 25,33</t>
+          <t>5,77; 25,4</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6,63; 26,52</t>
+          <t>6,71; 27,52</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,32; 17,41</t>
+          <t>3,21; 17,59</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,62; 18,12</t>
+          <t>3,43; 17,58</t>
         </is>
       </c>
     </row>
@@ -707,32 +707,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-7,91; 35,36</t>
+          <t>-8,51; 34,29</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-7,91; 35,69</t>
+          <t>-10,73; 33,65</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10,5; 62,75</t>
+          <t>11,14; 62,25</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12,78; 65,61</t>
+          <t>12,75; 66,56</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>6,38; 39,32</t>
+          <t>6,88; 40,23</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,81; 41,01</t>
+          <t>6,86; 40,9</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,86; 1,81</t>
+          <t>-2,86; 1,74</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,94; 2,43</t>
+          <t>-1,98; 2,68</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,27; 5,9</t>
+          <t>1,07; 5,81</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,25; 4,06</t>
+          <t>-1,49; 4,05</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,28; 3,16</t>
+          <t>-0,13; 3,19</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-1,17; 2,48</t>
+          <t>-0,97; 2,64</t>
         </is>
       </c>
     </row>
@@ -863,32 +863,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-2,91; 1,88</t>
+          <t>-2,93; 1,81</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-1,95; 2,52</t>
+          <t>-2,02; 2,8</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,32; 6,34</t>
+          <t>1,1; 6,23</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-1,28; 4,32</t>
+          <t>-1,54; 4,34</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-0,29; 3,32</t>
+          <t>-0,12; 3,34</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-1,2; 2,59</t>
+          <t>-1,0; 2,76</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,54; 2,45</t>
+          <t>-2,53; 2,65</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,97; 1,59</t>
+          <t>-4,06; 1,5</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,18; 6,52</t>
+          <t>-0,2; 6,52</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,73; 7,07</t>
+          <t>0,68; 7,12</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-0,58; 3,7</t>
+          <t>-0,43; 3,71</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-0,91; 3,4</t>
+          <t>-1,16; 3,48</t>
         </is>
       </c>
     </row>
@@ -1019,32 +1019,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-2,56; 2,52</t>
+          <t>-2,55; 2,74</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-4,03; 1,64</t>
+          <t>-4,12; 1,54</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-0,14; 7,16</t>
+          <t>-0,2; 7,1</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,76; 7,69</t>
+          <t>0,69; 7,71</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-0,59; 3,91</t>
+          <t>-0,44; 3,89</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-0,93; 3,6</t>
+          <t>-1,16; 3,67</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,47; 2,94</t>
+          <t>-2,87; 2,8</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,68; 3,51</t>
+          <t>-1,42; 3,43</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,21; 3,25</t>
+          <t>-2,1; 3,33</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-4,59; 2,02</t>
+          <t>-4,46; 1,86</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,54; 2,37</t>
+          <t>-1,54; 2,4</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-2,34; 1,75</t>
+          <t>-2,27; 1,84</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-2,52; 3,08</t>
+          <t>-2,91; 2,94</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-1,71; 3,68</t>
+          <t>-1,45; 3,6</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-2,24; 3,42</t>
+          <t>-2,15; 3,49</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-4,7; 2,11</t>
+          <t>-4,56; 1,92</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-1,57; 2,47</t>
+          <t>-1,57; 2,51</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-2,39; 1,83</t>
+          <t>-2,32; 1,91</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-3,92; 1,42</t>
+          <t>-3,74; 1,66</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-3,33; 1,96</t>
+          <t>-3,02; 2,2</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1,18; 6,28</t>
+          <t>0,97; 6,22</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1,33; 6,4</t>
+          <t>1,12; 6,27</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,55; 3,26</t>
+          <t>-0,55; 3,24</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-0,21; 3,52</t>
+          <t>0,02; 3,62</t>
         </is>
       </c>
     </row>
@@ -1331,32 +1331,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-4,27; 1,6</t>
+          <t>-4,13; 1,85</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-3,66; 2,2</t>
+          <t>-3,28; 2,47</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1,33; 7,29</t>
+          <t>1,13; 7,21</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1,49; 7,4</t>
+          <t>1,29; 7,37</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-0,62; 3,7</t>
+          <t>-0,61; 3,71</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-0,27; 3,99</t>
+          <t>0,01; 4,11</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP25-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IP25-Edad-trans_camb.xlsx
@@ -519,13 +519,13 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="F1" s="3" t="n"/>
@@ -593,22 +593,22 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>15,27</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>16,46</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>5,91</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>4,91</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>15,27</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>16,46</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-5,31; 15,2</t>
+          <t>5,82; 25,38</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-6,2; 15,33</t>
+          <t>7,1; 26,26</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5,77; 25,4</t>
+          <t>-5,62; 15,48</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6,71; 27,52</t>
+          <t>-5,65; 14,64</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,21; 17,59</t>
+          <t>3,38; 17,27</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,43; 17,58</t>
+          <t>3,51; 17,94</t>
         </is>
       </c>
     </row>
@@ -669,22 +669,22 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>33,19%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>35,79%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
           <t>11,59%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>9,63%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>33,19%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>35,79%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -707,32 +707,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-8,51; 34,29</t>
+          <t>10,76; 64,6</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-10,73; 33,65</t>
+          <t>13,67; 64,81</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11,14; 62,25</t>
+          <t>-9,42; 34,85</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12,75; 66,56</t>
+          <t>-9,86; 33,24</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>6,88; 40,23</t>
+          <t>6,44; 39,94</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,86; 40,9</t>
+          <t>6,32; 40,42</t>
         </is>
       </c>
     </row>
@@ -749,22 +749,22 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>3,39</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>1,29</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
           <t>-0,61</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>0,43</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>3,39</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>1,29</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,86; 1,74</t>
+          <t>1,46; 6,1</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,98; 2,68</t>
+          <t>-1,33; 4,04</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,07; 5,81</t>
+          <t>-2,95; 1,68</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,49; 4,05</t>
+          <t>-1,97; 2,84</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,13; 3,19</t>
+          <t>-0,07; 3,25</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,97; 2,64</t>
+          <t>-0,88; 2,55</t>
         </is>
       </c>
     </row>
@@ -825,22 +825,22 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>3,55%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1,35%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>-0,62%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>0,44%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>3,55%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>1,35%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -863,32 +863,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-2,93; 1,81</t>
+          <t>1,5; 6,57</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-2,02; 2,8</t>
+          <t>-1,3; 4,33</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,1; 6,23</t>
+          <t>-3,03; 1,74</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-1,54; 4,34</t>
+          <t>-2,02; 2,96</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-0,12; 3,34</t>
+          <t>-0,07; 3,39</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-1,0; 2,76</t>
+          <t>-0,9; 2,67</t>
         </is>
       </c>
     </row>
@@ -905,22 +905,22 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>2,95</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>3,57</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
           <t>-0,14</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>-1,37</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>2,95</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>3,57</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,53; 2,65</t>
+          <t>-0,38; 6,71</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-4,06; 1,5</t>
+          <t>0,65; 7,05</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,2; 6,52</t>
+          <t>-2,2; 3,04</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,68; 7,12</t>
+          <t>-3,93; 1,43</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-0,43; 3,71</t>
+          <t>-0,66; 3,69</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-1,16; 3,48</t>
+          <t>-0,98; 3,35</t>
         </is>
       </c>
     </row>
@@ -981,22 +981,22 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>3,1%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>3,75%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
           <t>-0,15%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>-1,39%</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>3,1%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>3,75%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1019,32 +1019,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-2,55; 2,74</t>
+          <t>-0,38; 7,24</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-4,12; 1,54</t>
+          <t>0,67; 7,78</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-0,2; 7,1</t>
+          <t>-2,2; 3,18</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,69; 7,71</t>
+          <t>-4,02; 1,44</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-0,44; 3,89</t>
+          <t>-0,67; 3,9</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-1,16; 3,67</t>
+          <t>-1,0; 3,51</t>
         </is>
       </c>
     </row>
@@ -1061,22 +1061,22 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>0,65</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-1,2</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
           <t>0,3</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>0,91</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>0,65</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-1,2</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,87; 2,8</t>
+          <t>-2,18; 3,06</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,42; 3,43</t>
+          <t>-4,52; 1,9</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,1; 3,33</t>
+          <t>-2,75; 2,77</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-4,46; 1,86</t>
+          <t>-1,55; 3,37</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,54; 2,4</t>
+          <t>-1,71; 2,38</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-2,27; 1,84</t>
+          <t>-2,15; 1,7</t>
         </is>
       </c>
     </row>
@@ -1137,22 +1137,22 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>0,67%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-1,24%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
           <t>0,31%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>0,94%</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>0,67%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>-1,24%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-2,91; 2,94</t>
+          <t>-2,24; 3,17</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-1,45; 3,6</t>
+          <t>-4,62; 2,0</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-2,15; 3,49</t>
+          <t>-2,8; 2,9</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-4,56; 1,92</t>
+          <t>-1,58; 3,54</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-1,57; 2,51</t>
+          <t>-1,74; 2,47</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-2,32; 1,91</t>
+          <t>-2,2; 1,76</t>
         </is>
       </c>
     </row>
@@ -1217,22 +1217,22 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>3,72</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>3,79</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
           <t>-1,23</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>-0,48</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>3,72</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>3,79</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-3,74; 1,66</t>
+          <t>1,28; 6,59</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-3,02; 2,2</t>
+          <t>1,31; 6,68</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,97; 6,22</t>
+          <t>-3,85; 1,47</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1,12; 6,27</t>
+          <t>-2,99; 2,18</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,55; 3,24</t>
+          <t>-0,53; 3,18</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,02; 3,62</t>
+          <t>-0,16; 3,5</t>
         </is>
       </c>
     </row>
@@ -1293,22 +1293,22 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>4,25%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>4,33%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
           <t>-1,36%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>-0,54%</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>4,25%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>4,33%</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -1331,32 +1331,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-4,13; 1,85</t>
+          <t>1,43; 7,75</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-3,28; 2,47</t>
+          <t>1,49; 7,84</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1,13; 7,21</t>
+          <t>-4,22; 1,66</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1,29; 7,37</t>
+          <t>-3,26; 2,46</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-0,61; 3,71</t>
+          <t>-0,6; 3,63</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0,01; 4,11</t>
+          <t>-0,17; 3,98</t>
         </is>
       </c>
     </row>
